--- a/artfynd/A 50261-2024 artfynd.xlsx
+++ b/artfynd/A 50261-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122748040</v>
+        <v>122748069</v>
       </c>
       <c r="B2" t="n">
-        <v>89991</v>
+        <v>79751</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1962</v>
+        <v>6456</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ängeskälen NV, Vb</t>
+          <t>Hocklet N, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>720066</v>
+        <v>720039</v>
       </c>
       <c r="R2" t="n">
-        <v>7214477</v>
+        <v>7214502</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122748067</v>
+        <v>122748076</v>
       </c>
       <c r="B3" t="n">
-        <v>82549</v>
+        <v>89995</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,34 +797,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>1962</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hocklet N, Vb</t>
+          <t>Tretjärnarna V, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720030</v>
+        <v>720162</v>
       </c>
       <c r="R3" t="n">
-        <v>7214500</v>
+        <v>7214448</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,11 +857,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ca 20 cm i diameter</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122748064</v>
+        <v>122748040</v>
       </c>
       <c r="B4" t="n">
-        <v>79747</v>
+        <v>89995</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,38 +899,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6456</v>
+        <v>1962</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hocklet N, Vb</t>
+          <t>Ängeskälen NV, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720010</v>
+        <v>720066</v>
       </c>
       <c r="R4" t="n">
-        <v>7214517</v>
+        <v>7214477</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122748083</v>
+        <v>122748104</v>
       </c>
       <c r="B5" t="n">
-        <v>89991</v>
+        <v>92225</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,38 +1005,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Källan N, Vb</t>
+          <t>Salaligan N, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720125</v>
+        <v>720064</v>
       </c>
       <c r="R5" t="n">
-        <v>7214437</v>
+        <v>7214317</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1104,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122748065</v>
+        <v>122748064</v>
       </c>
       <c r="B6" t="n">
-        <v>79747</v>
+        <v>79751</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,14 +1135,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Vb</t>
+          <t>Hocklet N, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720012</v>
+        <v>720010</v>
       </c>
       <c r="R6" t="n">
-        <v>7214506</v>
+        <v>7214517</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122748107</v>
+        <v>122748067</v>
       </c>
       <c r="B7" t="n">
-        <v>92221</v>
+        <v>82553</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,38 +1217,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Salaligan N, Vb</t>
+          <t>Hocklet N, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>720065</v>
+        <v>720030</v>
       </c>
       <c r="R7" t="n">
-        <v>7214297</v>
+        <v>7214500</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,6 +1281,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ca 20 cm i diameter</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1319,7 +1319,7 @@
         <v>122748085</v>
       </c>
       <c r="B8" t="n">
-        <v>90905</v>
+        <v>90909</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1422,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122748069</v>
+        <v>122748065</v>
       </c>
       <c r="B9" t="n">
-        <v>79747</v>
+        <v>79751</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1458,14 +1458,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hocklet N, Vb</t>
+          <t>Tretjärnarna V, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720039</v>
+        <v>720012</v>
       </c>
       <c r="R9" t="n">
-        <v>7214502</v>
+        <v>7214506</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1528,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122748055</v>
+        <v>122748083</v>
       </c>
       <c r="B10" t="n">
-        <v>98347</v>
+        <v>89995</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1540,38 +1540,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1962</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ängeskälen V, Vb</t>
+          <t>Källan N, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>719987</v>
+        <v>720125</v>
       </c>
       <c r="R10" t="n">
-        <v>7214787</v>
+        <v>7214437</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1634,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122748104</v>
+        <v>122748055</v>
       </c>
       <c r="B11" t="n">
-        <v>92221</v>
+        <v>98355</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1646,38 +1646,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Salaligan N, Vb</t>
+          <t>Ängeskälen V, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>720064</v>
+        <v>719987</v>
       </c>
       <c r="R11" t="n">
-        <v>7214317</v>
+        <v>7214787</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1740,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122748076</v>
+        <v>122748107</v>
       </c>
       <c r="B12" t="n">
-        <v>89991</v>
+        <v>92225</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Vb</t>
+          <t>Salaligan N, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>720162</v>
+        <v>720065</v>
       </c>
       <c r="R12" t="n">
-        <v>7214448</v>
+        <v>7214297</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 50261-2024 artfynd.xlsx
+++ b/artfynd/A 50261-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122748069</v>
+        <v>122748067</v>
       </c>
       <c r="B2" t="n">
-        <v>79751</v>
+        <v>82553</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>720039</v>
+        <v>720030</v>
       </c>
       <c r="R2" t="n">
-        <v>7214502</v>
+        <v>7214500</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ca 20 cm i diameter</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122748076</v>
+        <v>122748104</v>
       </c>
       <c r="B3" t="n">
-        <v>89995</v>
+        <v>92225</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,38 +798,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Vb</t>
+          <t>Salaligan N, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720162</v>
+        <v>720064</v>
       </c>
       <c r="R3" t="n">
-        <v>7214448</v>
+        <v>7214317</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122748040</v>
+        <v>122748069</v>
       </c>
       <c r="B4" t="n">
-        <v>89995</v>
+        <v>79751</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,38 +904,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1962</v>
+        <v>6456</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ängeskälen NV, Vb</t>
+          <t>Hocklet N, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720066</v>
+        <v>720039</v>
       </c>
       <c r="R4" t="n">
-        <v>7214477</v>
+        <v>7214502</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122748104</v>
+        <v>122748065</v>
       </c>
       <c r="B5" t="n">
-        <v>92225</v>
+        <v>79751</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,34 +1014,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>6456</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Salaligan N, Vb</t>
+          <t>Tretjärnarna V, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720064</v>
+        <v>720012</v>
       </c>
       <c r="R5" t="n">
-        <v>7214317</v>
+        <v>7214506</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122748064</v>
+        <v>122748040</v>
       </c>
       <c r="B6" t="n">
-        <v>79751</v>
+        <v>89995</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,38 +1116,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>1962</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hocklet N, Vb</t>
+          <t>Ängeskälen NV, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720010</v>
+        <v>720066</v>
       </c>
       <c r="R6" t="n">
-        <v>7214517</v>
+        <v>7214477</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122748067</v>
+        <v>122748076</v>
       </c>
       <c r="B7" t="n">
-        <v>82553</v>
+        <v>89995</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,34 +1226,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>1962</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hocklet N, Vb</t>
+          <t>Tretjärnarna V, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>720030</v>
+        <v>720162</v>
       </c>
       <c r="R7" t="n">
-        <v>7214500</v>
+        <v>7214448</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,11 +1286,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ca 20 cm i diameter</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1316,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122748085</v>
+        <v>122748083</v>
       </c>
       <c r="B8" t="n">
-        <v>90909</v>
+        <v>89995</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,25 +1328,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>1962</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1359,7 +1359,7 @@
         <v>720125</v>
       </c>
       <c r="R8" t="n">
-        <v>7214439</v>
+        <v>7214437</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122748065</v>
+        <v>122748085</v>
       </c>
       <c r="B9" t="n">
-        <v>79751</v>
+        <v>90909</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1438,34 +1438,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6456</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Vb</t>
+          <t>Källan N, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720012</v>
+        <v>720125</v>
       </c>
       <c r="R9" t="n">
-        <v>7214506</v>
+        <v>7214439</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1528,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122748083</v>
+        <v>122748055</v>
       </c>
       <c r="B10" t="n">
-        <v>89995</v>
+        <v>98355</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1540,38 +1540,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1962</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Källan N, Vb</t>
+          <t>Ängeskälen V, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>720125</v>
+        <v>719987</v>
       </c>
       <c r="R10" t="n">
-        <v>7214437</v>
+        <v>7214787</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1634,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122748055</v>
+        <v>122748064</v>
       </c>
       <c r="B11" t="n">
-        <v>98355</v>
+        <v>79751</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1646,38 +1646,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ängeskälen V, Vb</t>
+          <t>Hocklet N, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>719987</v>
+        <v>720010</v>
       </c>
       <c r="R11" t="n">
-        <v>7214787</v>
+        <v>7214517</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 50261-2024 artfynd.xlsx
+++ b/artfynd/A 50261-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122748067</v>
+        <v>122748065</v>
       </c>
       <c r="B2" t="n">
-        <v>82553</v>
+        <v>79751</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>6456</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hocklet N, Vb</t>
+          <t>Tretjärnarna V, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>720030</v>
+        <v>720012</v>
       </c>
       <c r="R2" t="n">
-        <v>7214500</v>
+        <v>7214506</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ca 20 cm i diameter</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122748104</v>
+        <v>122748067</v>
       </c>
       <c r="B3" t="n">
-        <v>92225</v>
+        <v>82553</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,38 +793,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Salaligan N, Vb</t>
+          <t>Hocklet N, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720064</v>
+        <v>720030</v>
       </c>
       <c r="R3" t="n">
-        <v>7214317</v>
+        <v>7214500</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,6 +857,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ca 20 cm i diameter</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122748069</v>
+        <v>122748055</v>
       </c>
       <c r="B4" t="n">
-        <v>79751</v>
+        <v>98357</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,38 +904,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hocklet N, Vb</t>
+          <t>Ängeskälen V, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720039</v>
+        <v>719987</v>
       </c>
       <c r="R4" t="n">
-        <v>7214502</v>
+        <v>7214787</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,7 +998,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122748065</v>
+        <v>122748064</v>
       </c>
       <c r="B5" t="n">
         <v>79751</v>
@@ -1034,14 +1034,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Vb</t>
+          <t>Hocklet N, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720012</v>
+        <v>720010</v>
       </c>
       <c r="R5" t="n">
-        <v>7214506</v>
+        <v>7214517</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1104,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122748040</v>
+        <v>122748104</v>
       </c>
       <c r="B6" t="n">
-        <v>89995</v>
+        <v>92225</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1116,38 +1116,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ängeskälen NV, Vb</t>
+          <t>Salaligan N, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720066</v>
+        <v>720064</v>
       </c>
       <c r="R6" t="n">
-        <v>7214477</v>
+        <v>7214317</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122748076</v>
+        <v>122748107</v>
       </c>
       <c r="B7" t="n">
-        <v>89995</v>
+        <v>92225</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,38 +1222,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Vb</t>
+          <t>Salaligan N, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>720162</v>
+        <v>720065</v>
       </c>
       <c r="R7" t="n">
-        <v>7214448</v>
+        <v>7214297</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1316,7 +1316,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122748083</v>
+        <v>122748076</v>
       </c>
       <c r="B8" t="n">
         <v>89995</v>
@@ -1352,14 +1352,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Källan N, Vb</t>
+          <t>Tretjärnarna V, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>720125</v>
+        <v>720162</v>
       </c>
       <c r="R8" t="n">
-        <v>7214437</v>
+        <v>7214448</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1528,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122748055</v>
+        <v>122748040</v>
       </c>
       <c r="B10" t="n">
-        <v>98355</v>
+        <v>89995</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1540,38 +1540,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1962</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ängeskälen V, Vb</t>
+          <t>Ängeskälen NV, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>719987</v>
+        <v>720066</v>
       </c>
       <c r="R10" t="n">
-        <v>7214787</v>
+        <v>7214477</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1634,7 +1634,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122748064</v>
+        <v>122748069</v>
       </c>
       <c r="B11" t="n">
         <v>79751</v>
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>720010</v>
+        <v>720039</v>
       </c>
       <c r="R11" t="n">
-        <v>7214517</v>
+        <v>7214502</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1740,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122748107</v>
+        <v>122748083</v>
       </c>
       <c r="B12" t="n">
-        <v>92225</v>
+        <v>89995</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Salaligan N, Vb</t>
+          <t>Källan N, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>720065</v>
+        <v>720125</v>
       </c>
       <c r="R12" t="n">
-        <v>7214297</v>
+        <v>7214437</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 50261-2024 artfynd.xlsx
+++ b/artfynd/A 50261-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122748065</v>
+        <v>122748083</v>
       </c>
       <c r="B2" t="n">
-        <v>79751</v>
+        <v>89995</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>1962</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Vb</t>
+          <t>Källan N, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>720012</v>
+        <v>720125</v>
       </c>
       <c r="R2" t="n">
-        <v>7214506</v>
+        <v>7214437</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122748055</v>
+        <v>122748104</v>
       </c>
       <c r="B4" t="n">
-        <v>98357</v>
+        <v>92225</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,38 +904,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ängeskälen V, Vb</t>
+          <t>Salaligan N, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>719987</v>
+        <v>720064</v>
       </c>
       <c r="R4" t="n">
-        <v>7214787</v>
+        <v>7214317</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122748064</v>
+        <v>122748040</v>
       </c>
       <c r="B5" t="n">
-        <v>79751</v>
+        <v>89995</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,38 +1010,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>1962</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hocklet N, Vb</t>
+          <t>Ängeskälen NV, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720010</v>
+        <v>720066</v>
       </c>
       <c r="R5" t="n">
-        <v>7214517</v>
+        <v>7214477</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1104,7 +1104,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122748104</v>
+        <v>122748107</v>
       </c>
       <c r="B6" t="n">
         <v>92225</v>
@@ -1144,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720064</v>
+        <v>720065</v>
       </c>
       <c r="R6" t="n">
-        <v>7214317</v>
+        <v>7214297</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122748107</v>
+        <v>122748085</v>
       </c>
       <c r="B7" t="n">
-        <v>92225</v>
+        <v>90909</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,34 +1226,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Salaligan N, Vb</t>
+          <t>Källan N, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>720065</v>
+        <v>720125</v>
       </c>
       <c r="R7" t="n">
-        <v>7214297</v>
+        <v>7214439</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1316,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122748076</v>
+        <v>122748065</v>
       </c>
       <c r="B8" t="n">
-        <v>89995</v>
+        <v>79751</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,25 +1328,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1962</v>
+        <v>6456</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>720162</v>
+        <v>720012</v>
       </c>
       <c r="R8" t="n">
-        <v>7214448</v>
+        <v>7214506</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122748085</v>
+        <v>122748076</v>
       </c>
       <c r="B9" t="n">
-        <v>90909</v>
+        <v>89995</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,38 +1434,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>1962</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Källan N, Vb</t>
+          <t>Tretjärnarna V, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720125</v>
+        <v>720162</v>
       </c>
       <c r="R9" t="n">
-        <v>7214439</v>
+        <v>7214448</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1528,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122748040</v>
+        <v>122748069</v>
       </c>
       <c r="B10" t="n">
-        <v>89995</v>
+        <v>79751</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1540,38 +1540,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1962</v>
+        <v>6456</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ängeskälen NV, Vb</t>
+          <t>Hocklet N, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>720066</v>
+        <v>720039</v>
       </c>
       <c r="R10" t="n">
-        <v>7214477</v>
+        <v>7214502</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1634,7 +1634,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122748069</v>
+        <v>122748064</v>
       </c>
       <c r="B11" t="n">
         <v>79751</v>
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>720039</v>
+        <v>720010</v>
       </c>
       <c r="R11" t="n">
-        <v>7214502</v>
+        <v>7214517</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1740,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122748083</v>
+        <v>122748055</v>
       </c>
       <c r="B12" t="n">
-        <v>89995</v>
+        <v>98357</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1962</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Källan N, Vb</t>
+          <t>Ängeskälen V, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>720125</v>
+        <v>719987</v>
       </c>
       <c r="R12" t="n">
-        <v>7214437</v>
+        <v>7214787</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 50261-2024 artfynd.xlsx
+++ b/artfynd/A 50261-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122748083</v>
+        <v>122748065</v>
       </c>
       <c r="B2" t="n">
-        <v>89995</v>
+        <v>79751</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1962</v>
+        <v>6456</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Källan N, Vb</t>
+          <t>Tretjärnarna V, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>720125</v>
+        <v>720012</v>
       </c>
       <c r="R2" t="n">
-        <v>7214437</v>
+        <v>7214506</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122748067</v>
+        <v>122748069</v>
       </c>
       <c r="B3" t="n">
-        <v>82553</v>
+        <v>79751</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720030</v>
+        <v>720039</v>
       </c>
       <c r="R3" t="n">
-        <v>7214500</v>
+        <v>7214502</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,11 +857,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ca 20 cm i diameter</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122748104</v>
+        <v>122748076</v>
       </c>
       <c r="B4" t="n">
-        <v>92225</v>
+        <v>89995</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,38 +899,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Salaligan N, Vb</t>
+          <t>Tretjärnarna V, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720064</v>
+        <v>720162</v>
       </c>
       <c r="R4" t="n">
-        <v>7214317</v>
+        <v>7214448</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1104,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122748107</v>
+        <v>122748064</v>
       </c>
       <c r="B6" t="n">
-        <v>92225</v>
+        <v>79751</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1120,34 +1115,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>6456</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Salaligan N, Vb</t>
+          <t>Hocklet N, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720065</v>
+        <v>720010</v>
       </c>
       <c r="R6" t="n">
-        <v>7214297</v>
+        <v>7214517</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122748085</v>
+        <v>122748055</v>
       </c>
       <c r="B7" t="n">
-        <v>90909</v>
+        <v>98365</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,38 +1217,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Källan N, Vb</t>
+          <t>Ängeskälen V, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>720125</v>
+        <v>719987</v>
       </c>
       <c r="R7" t="n">
-        <v>7214439</v>
+        <v>7214787</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1316,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122748065</v>
+        <v>122748067</v>
       </c>
       <c r="B8" t="n">
-        <v>79751</v>
+        <v>82553</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,38 +1323,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6456</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Vb</t>
+          <t>Hocklet N, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>720012</v>
+        <v>720030</v>
       </c>
       <c r="R8" t="n">
-        <v>7214506</v>
+        <v>7214500</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,6 +1387,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ca 20 cm i diameter</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1422,7 +1422,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122748076</v>
+        <v>122748083</v>
       </c>
       <c r="B9" t="n">
         <v>89995</v>
@@ -1458,14 +1458,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Vb</t>
+          <t>Källan N, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720162</v>
+        <v>720125</v>
       </c>
       <c r="R9" t="n">
-        <v>7214448</v>
+        <v>7214437</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1528,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122748069</v>
+        <v>122748085</v>
       </c>
       <c r="B10" t="n">
-        <v>79751</v>
+        <v>90917</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1544,34 +1544,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6456</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hocklet N, Vb</t>
+          <t>Källan N, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>720039</v>
+        <v>720125</v>
       </c>
       <c r="R10" t="n">
-        <v>7214502</v>
+        <v>7214439</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1634,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122748064</v>
+        <v>122748107</v>
       </c>
       <c r="B11" t="n">
-        <v>79751</v>
+        <v>92233</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1650,34 +1650,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6456</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hocklet N, Vb</t>
+          <t>Salaligan N, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>720010</v>
+        <v>720065</v>
       </c>
       <c r="R11" t="n">
-        <v>7214517</v>
+        <v>7214297</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1740,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122748055</v>
+        <v>122748104</v>
       </c>
       <c r="B12" t="n">
-        <v>98357</v>
+        <v>92233</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ängeskälen V, Vb</t>
+          <t>Salaligan N, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>719987</v>
+        <v>720064</v>
       </c>
       <c r="R12" t="n">
-        <v>7214787</v>
+        <v>7214317</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 50261-2024 artfynd.xlsx
+++ b/artfynd/A 50261-2024 artfynd.xlsx
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122748064</v>
+        <v>122748067</v>
       </c>
       <c r="B6" t="n">
-        <v>79751</v>
+        <v>82553</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720010</v>
+        <v>720030</v>
       </c>
       <c r="R6" t="n">
-        <v>7214517</v>
+        <v>7214500</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1175,6 +1175,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ca 20 cm i diameter</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122748055</v>
+        <v>122748064</v>
       </c>
       <c r="B7" t="n">
-        <v>98365</v>
+        <v>79751</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,38 +1222,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ängeskälen V, Vb</t>
+          <t>Hocklet N, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>719987</v>
+        <v>720010</v>
       </c>
       <c r="R7" t="n">
-        <v>7214787</v>
+        <v>7214517</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122748067</v>
+        <v>122748055</v>
       </c>
       <c r="B8" t="n">
-        <v>82553</v>
+        <v>98365</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,38 +1328,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hocklet N, Vb</t>
+          <t>Ängeskälen V, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>720030</v>
+        <v>719987</v>
       </c>
       <c r="R8" t="n">
-        <v>7214500</v>
+        <v>7214787</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,11 +1392,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ca 20 cm i diameter</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 50261-2024 artfynd.xlsx
+++ b/artfynd/A 50261-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122748065</v>
+        <v>122748085</v>
       </c>
       <c r="B2" t="n">
-        <v>79751</v>
+        <v>90917</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Vb</t>
+          <t>Källan N, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>720012</v>
+        <v>720125</v>
       </c>
       <c r="R2" t="n">
-        <v>7214506</v>
+        <v>7214439</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122748069</v>
+        <v>122748104</v>
       </c>
       <c r="B3" t="n">
-        <v>79751</v>
+        <v>92233</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,34 +797,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hocklet N, Vb</t>
+          <t>Salaligan N, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720039</v>
+        <v>720064</v>
       </c>
       <c r="R3" t="n">
-        <v>7214502</v>
+        <v>7214317</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122748040</v>
+        <v>122748107</v>
       </c>
       <c r="B5" t="n">
-        <v>89995</v>
+        <v>92233</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,38 +1005,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ängeskälen NV, Vb</t>
+          <t>Salaligan N, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720066</v>
+        <v>720065</v>
       </c>
       <c r="R5" t="n">
-        <v>7214477</v>
+        <v>7214297</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122748067</v>
+        <v>122748069</v>
       </c>
       <c r="B6" t="n">
-        <v>82553</v>
+        <v>79751</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>6456</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720030</v>
+        <v>720039</v>
       </c>
       <c r="R6" t="n">
-        <v>7214500</v>
+        <v>7214502</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1175,11 +1175,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ca 20 cm i diameter</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122748064</v>
+        <v>122748065</v>
       </c>
       <c r="B7" t="n">
         <v>79751</v>
@@ -1246,14 +1241,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hocklet N, Vb</t>
+          <t>Tretjärnarna V, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>720010</v>
+        <v>720012</v>
       </c>
       <c r="R7" t="n">
-        <v>7214517</v>
+        <v>7214506</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1422,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122748083</v>
+        <v>122748067</v>
       </c>
       <c r="B9" t="n">
-        <v>89995</v>
+        <v>82553</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1438,34 +1433,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1962</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Källan N, Vb</t>
+          <t>Hocklet N, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720125</v>
+        <v>720030</v>
       </c>
       <c r="R9" t="n">
-        <v>7214437</v>
+        <v>7214500</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1498,6 +1493,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ca 20 cm i diameter</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1528,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122748085</v>
+        <v>122748040</v>
       </c>
       <c r="B10" t="n">
-        <v>90917</v>
+        <v>89995</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1540,38 +1540,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>1962</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Källan N, Vb</t>
+          <t>Ängeskälen NV, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>720125</v>
+        <v>720066</v>
       </c>
       <c r="R10" t="n">
-        <v>7214439</v>
+        <v>7214477</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1634,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122748107</v>
+        <v>122748083</v>
       </c>
       <c r="B11" t="n">
-        <v>92233</v>
+        <v>89995</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1646,38 +1646,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Salaligan N, Vb</t>
+          <t>Källan N, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>720065</v>
+        <v>720125</v>
       </c>
       <c r="R11" t="n">
-        <v>7214297</v>
+        <v>7214437</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1740,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122748104</v>
+        <v>122748064</v>
       </c>
       <c r="B12" t="n">
-        <v>92233</v>
+        <v>79751</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1756,34 +1756,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>6456</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Salaligan N, Vb</t>
+          <t>Hocklet N, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>720064</v>
+        <v>720010</v>
       </c>
       <c r="R12" t="n">
-        <v>7214317</v>
+        <v>7214517</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 50261-2024 artfynd.xlsx
+++ b/artfynd/A 50261-2024 artfynd.xlsx
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122748076</v>
+        <v>122748107</v>
       </c>
       <c r="B4" t="n">
-        <v>89995</v>
+        <v>92233</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,38 +899,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Vb</t>
+          <t>Salaligan N, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720162</v>
+        <v>720065</v>
       </c>
       <c r="R4" t="n">
-        <v>7214448</v>
+        <v>7214297</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122748107</v>
+        <v>122748076</v>
       </c>
       <c r="B5" t="n">
-        <v>92233</v>
+        <v>89995</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,38 +1005,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Salaligan N, Vb</t>
+          <t>Tretjärnarna V, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720065</v>
+        <v>720162</v>
       </c>
       <c r="R5" t="n">
-        <v>7214297</v>
+        <v>7214448</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 50261-2024 artfynd.xlsx
+++ b/artfynd/A 50261-2024 artfynd.xlsx
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122748107</v>
+        <v>122748076</v>
       </c>
       <c r="B4" t="n">
-        <v>92233</v>
+        <v>89995</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,38 +899,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Salaligan N, Vb</t>
+          <t>Tretjärnarna V, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720065</v>
+        <v>720162</v>
       </c>
       <c r="R4" t="n">
-        <v>7214297</v>
+        <v>7214448</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122748076</v>
+        <v>122748107</v>
       </c>
       <c r="B5" t="n">
-        <v>89995</v>
+        <v>92233</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,38 +1005,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Vb</t>
+          <t>Salaligan N, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720162</v>
+        <v>720065</v>
       </c>
       <c r="R5" t="n">
-        <v>7214448</v>
+        <v>7214297</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 50261-2024 artfynd.xlsx
+++ b/artfynd/A 50261-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122748085</v>
+        <v>122748069</v>
       </c>
       <c r="B2" t="n">
-        <v>90917</v>
+        <v>79751</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>6456</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Källan N, Vb</t>
+          <t>Hocklet N, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>720125</v>
+        <v>720039</v>
       </c>
       <c r="R2" t="n">
-        <v>7214439</v>
+        <v>7214502</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122748104</v>
+        <v>122748064</v>
       </c>
       <c r="B3" t="n">
-        <v>92233</v>
+        <v>79751</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,34 +797,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Salaligan N, Vb</t>
+          <t>Hocklet N, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720064</v>
+        <v>720010</v>
       </c>
       <c r="R3" t="n">
-        <v>7214317</v>
+        <v>7214517</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122748076</v>
+        <v>122748067</v>
       </c>
       <c r="B4" t="n">
-        <v>89995</v>
+        <v>82553</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,34 +903,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1962</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Vb</t>
+          <t>Hocklet N, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720162</v>
+        <v>720030</v>
       </c>
       <c r="R4" t="n">
-        <v>7214448</v>
+        <v>7214500</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,6 +963,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ca 20 cm i diameter</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122748107</v>
+        <v>122748076</v>
       </c>
       <c r="B5" t="n">
-        <v>92233</v>
+        <v>89995</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,38 +1010,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Salaligan N, Vb</t>
+          <t>Tretjärnarna V, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720065</v>
+        <v>720162</v>
       </c>
       <c r="R5" t="n">
-        <v>7214297</v>
+        <v>7214448</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122748069</v>
+        <v>122748104</v>
       </c>
       <c r="B6" t="n">
-        <v>79751</v>
+        <v>92233</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,34 +1120,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hocklet N, Vb</t>
+          <t>Salaligan N, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720039</v>
+        <v>720064</v>
       </c>
       <c r="R6" t="n">
-        <v>7214502</v>
+        <v>7214317</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122748065</v>
+        <v>122748040</v>
       </c>
       <c r="B7" t="n">
-        <v>79751</v>
+        <v>89995</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,38 +1222,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6456</v>
+        <v>1962</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Vb</t>
+          <t>Ängeskälen NV, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>720012</v>
+        <v>720066</v>
       </c>
       <c r="R7" t="n">
-        <v>7214506</v>
+        <v>7214477</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122748055</v>
+        <v>122748065</v>
       </c>
       <c r="B8" t="n">
-        <v>98365</v>
+        <v>79751</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,38 +1328,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ängeskälen V, Vb</t>
+          <t>Tretjärnarna V, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>719987</v>
+        <v>720012</v>
       </c>
       <c r="R8" t="n">
-        <v>7214787</v>
+        <v>7214506</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122748067</v>
+        <v>122748055</v>
       </c>
       <c r="B9" t="n">
-        <v>82553</v>
+        <v>98365</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,38 +1434,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hocklet N, Vb</t>
+          <t>Ängeskälen V, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720030</v>
+        <v>719987</v>
       </c>
       <c r="R9" t="n">
-        <v>7214500</v>
+        <v>7214787</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1493,11 +1498,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ca 20 cm i diameter</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1528,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122748040</v>
+        <v>122748107</v>
       </c>
       <c r="B10" t="n">
-        <v>89995</v>
+        <v>92233</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1540,38 +1540,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ängeskälen NV, Vb</t>
+          <t>Salaligan N, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>720066</v>
+        <v>720065</v>
       </c>
       <c r="R10" t="n">
-        <v>7214477</v>
+        <v>7214297</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1634,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122748083</v>
+        <v>122748085</v>
       </c>
       <c r="B11" t="n">
-        <v>89995</v>
+        <v>90917</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1646,25 +1646,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1962</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1677,7 +1677,7 @@
         <v>720125</v>
       </c>
       <c r="R11" t="n">
-        <v>7214437</v>
+        <v>7214439</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1740,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122748064</v>
+        <v>122748083</v>
       </c>
       <c r="B12" t="n">
-        <v>79751</v>
+        <v>89995</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6456</v>
+        <v>1962</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hocklet N, Vb</t>
+          <t>Källan N, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>720010</v>
+        <v>720125</v>
       </c>
       <c r="R12" t="n">
-        <v>7214517</v>
+        <v>7214437</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 50261-2024 artfynd.xlsx
+++ b/artfynd/A 50261-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122748069</v>
+        <v>122748107</v>
       </c>
       <c r="B2" t="n">
-        <v>79751</v>
+        <v>92233</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hocklet N, Vb</t>
+          <t>Salaligan N, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>720039</v>
+        <v>720065</v>
       </c>
       <c r="R2" t="n">
-        <v>7214502</v>
+        <v>7214297</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122748064</v>
+        <v>122748085</v>
       </c>
       <c r="B3" t="n">
-        <v>79751</v>
+        <v>90917</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,34 +797,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hocklet N, Vb</t>
+          <t>Källan N, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720010</v>
+        <v>720125</v>
       </c>
       <c r="R3" t="n">
-        <v>7214517</v>
+        <v>7214439</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122748067</v>
+        <v>122748040</v>
       </c>
       <c r="B4" t="n">
-        <v>82553</v>
+        <v>89995</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,34 +903,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>1962</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hocklet N, Vb</t>
+          <t>Ängeskälen NV, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720030</v>
+        <v>720066</v>
       </c>
       <c r="R4" t="n">
-        <v>7214500</v>
+        <v>7214477</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,11 +963,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ca 20 cm i diameter</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122748076</v>
+        <v>122748069</v>
       </c>
       <c r="B5" t="n">
-        <v>89995</v>
+        <v>79751</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,38 +1005,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1962</v>
+        <v>6456</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Vb</t>
+          <t>Hocklet N, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720162</v>
+        <v>720039</v>
       </c>
       <c r="R5" t="n">
-        <v>7214448</v>
+        <v>7214502</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1210,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122748040</v>
+        <v>122748064</v>
       </c>
       <c r="B7" t="n">
-        <v>89995</v>
+        <v>79751</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,38 +1217,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1962</v>
+        <v>6456</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ängeskälen NV, Vb</t>
+          <t>Hocklet N, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>720066</v>
+        <v>720010</v>
       </c>
       <c r="R7" t="n">
-        <v>7214477</v>
+        <v>7214517</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1316,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122748065</v>
+        <v>122748076</v>
       </c>
       <c r="B8" t="n">
-        <v>79751</v>
+        <v>89995</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,25 +1323,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6456</v>
+        <v>1962</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>720012</v>
+        <v>720162</v>
       </c>
       <c r="R8" t="n">
-        <v>7214506</v>
+        <v>7214448</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122748055</v>
+        <v>122748067</v>
       </c>
       <c r="B9" t="n">
-        <v>98365</v>
+        <v>82553</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,38 +1429,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ängeskälen V, Vb</t>
+          <t>Hocklet N, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>719987</v>
+        <v>720030</v>
       </c>
       <c r="R9" t="n">
-        <v>7214787</v>
+        <v>7214500</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1498,6 +1493,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ca 20 cm i diameter</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1528,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122748107</v>
+        <v>122748083</v>
       </c>
       <c r="B10" t="n">
-        <v>92233</v>
+        <v>89995</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1540,38 +1540,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Salaligan N, Vb</t>
+          <t>Källan N, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>720065</v>
+        <v>720125</v>
       </c>
       <c r="R10" t="n">
-        <v>7214297</v>
+        <v>7214437</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1634,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122748085</v>
+        <v>122748055</v>
       </c>
       <c r="B11" t="n">
-        <v>90917</v>
+        <v>98365</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1646,38 +1646,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Källan N, Vb</t>
+          <t>Ängeskälen V, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>720125</v>
+        <v>719987</v>
       </c>
       <c r="R11" t="n">
-        <v>7214439</v>
+        <v>7214787</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1740,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122748083</v>
+        <v>122748065</v>
       </c>
       <c r="B12" t="n">
-        <v>89995</v>
+        <v>79751</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1962</v>
+        <v>6456</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Källan N, Vb</t>
+          <t>Tretjärnarna V, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>720125</v>
+        <v>720012</v>
       </c>
       <c r="R12" t="n">
-        <v>7214437</v>
+        <v>7214506</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 50261-2024 artfynd.xlsx
+++ b/artfynd/A 50261-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122748107</v>
+        <v>122748067</v>
       </c>
       <c r="B2" t="n">
-        <v>92233</v>
+        <v>82556</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Salaligan N, Vb</t>
+          <t>Hocklet N, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>720065</v>
+        <v>720030</v>
       </c>
       <c r="R2" t="n">
-        <v>7214297</v>
+        <v>7214500</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ca 20 cm i diameter</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122748085</v>
+        <v>122748076</v>
       </c>
       <c r="B3" t="n">
-        <v>90917</v>
+        <v>89998</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,38 +798,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>1962</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Källan N, Vb</t>
+          <t>Tretjärnarna V, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720125</v>
+        <v>720162</v>
       </c>
       <c r="R3" t="n">
-        <v>7214439</v>
+        <v>7214448</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122748040</v>
+        <v>122748104</v>
       </c>
       <c r="B4" t="n">
-        <v>89995</v>
+        <v>92236</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,38 +904,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ängeskälen NV, Vb</t>
+          <t>Salaligan N, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720066</v>
+        <v>720064</v>
       </c>
       <c r="R4" t="n">
-        <v>7214477</v>
+        <v>7214317</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122748069</v>
+        <v>122748065</v>
       </c>
       <c r="B5" t="n">
-        <v>79751</v>
+        <v>79754</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,14 +1034,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hocklet N, Vb</t>
+          <t>Tretjärnarna V, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720039</v>
+        <v>720012</v>
       </c>
       <c r="R5" t="n">
-        <v>7214502</v>
+        <v>7214506</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122748104</v>
+        <v>122748055</v>
       </c>
       <c r="B6" t="n">
-        <v>92233</v>
+        <v>98368</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,38 +1116,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Salaligan N, Vb</t>
+          <t>Ängeskälen V, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720064</v>
+        <v>719987</v>
       </c>
       <c r="R6" t="n">
-        <v>7214317</v>
+        <v>7214787</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122748064</v>
+        <v>122748085</v>
       </c>
       <c r="B7" t="n">
-        <v>79751</v>
+        <v>90920</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,34 +1226,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6456</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hocklet N, Vb</t>
+          <t>Källan N, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>720010</v>
+        <v>720125</v>
       </c>
       <c r="R7" t="n">
-        <v>7214517</v>
+        <v>7214439</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122748076</v>
+        <v>122748083</v>
       </c>
       <c r="B8" t="n">
-        <v>89995</v>
+        <v>89998</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1347,14 +1352,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Vb</t>
+          <t>Källan N, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>720162</v>
+        <v>720125</v>
       </c>
       <c r="R8" t="n">
-        <v>7214448</v>
+        <v>7214437</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122748067</v>
+        <v>122748107</v>
       </c>
       <c r="B9" t="n">
-        <v>82553</v>
+        <v>92236</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,38 +1434,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hocklet N, Vb</t>
+          <t>Salaligan N, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720030</v>
+        <v>720065</v>
       </c>
       <c r="R9" t="n">
-        <v>7214500</v>
+        <v>7214297</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1493,11 +1498,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ca 20 cm i diameter</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1528,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122748083</v>
+        <v>122748069</v>
       </c>
       <c r="B10" t="n">
-        <v>89995</v>
+        <v>79754</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1540,38 +1540,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1962</v>
+        <v>6456</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Källan N, Vb</t>
+          <t>Hocklet N, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>720125</v>
+        <v>720039</v>
       </c>
       <c r="R10" t="n">
-        <v>7214437</v>
+        <v>7214502</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1634,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122748055</v>
+        <v>122748064</v>
       </c>
       <c r="B11" t="n">
-        <v>98365</v>
+        <v>79754</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1646,38 +1646,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ängeskälen V, Vb</t>
+          <t>Hocklet N, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>719987</v>
+        <v>720010</v>
       </c>
       <c r="R11" t="n">
-        <v>7214787</v>
+        <v>7214517</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1740,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122748065</v>
+        <v>122748040</v>
       </c>
       <c r="B12" t="n">
-        <v>79751</v>
+        <v>89998</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6456</v>
+        <v>1962</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Vb</t>
+          <t>Ängeskälen NV, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>720012</v>
+        <v>720066</v>
       </c>
       <c r="R12" t="n">
-        <v>7214506</v>
+        <v>7214477</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 50261-2024 artfynd.xlsx
+++ b/artfynd/A 50261-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122748067</v>
+        <v>122748104</v>
       </c>
       <c r="B2" t="n">
-        <v>82556</v>
+        <v>92238</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hocklet N, Vb</t>
+          <t>Salaligan N, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>720030</v>
+        <v>720064</v>
       </c>
       <c r="R2" t="n">
-        <v>7214500</v>
+        <v>7214317</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ca 20 cm i diameter</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122748076</v>
+        <v>122748055</v>
       </c>
       <c r="B3" t="n">
-        <v>89998</v>
+        <v>98370</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,38 +793,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1962</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Vb</t>
+          <t>Ängeskälen V, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720162</v>
+        <v>719987</v>
       </c>
       <c r="R3" t="n">
-        <v>7214448</v>
+        <v>7214787</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122748104</v>
+        <v>122748065</v>
       </c>
       <c r="B4" t="n">
-        <v>92236</v>
+        <v>79756</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,34 +903,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6456</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Salaligan N, Vb</t>
+          <t>Tretjärnarna V, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720064</v>
+        <v>720012</v>
       </c>
       <c r="R4" t="n">
-        <v>7214317</v>
+        <v>7214506</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122748065</v>
+        <v>122748083</v>
       </c>
       <c r="B5" t="n">
-        <v>79754</v>
+        <v>90000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,38 +1005,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>1962</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Vb</t>
+          <t>Källan N, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720012</v>
+        <v>720125</v>
       </c>
       <c r="R5" t="n">
-        <v>7214506</v>
+        <v>7214437</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1104,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122748055</v>
+        <v>122748076</v>
       </c>
       <c r="B6" t="n">
-        <v>98368</v>
+        <v>90000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1116,38 +1111,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1962</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ängeskälen V, Vb</t>
+          <t>Tretjärnarna V, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>719987</v>
+        <v>720162</v>
       </c>
       <c r="R6" t="n">
-        <v>7214787</v>
+        <v>7214448</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122748085</v>
+        <v>122748040</v>
       </c>
       <c r="B7" t="n">
-        <v>90920</v>
+        <v>90000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,38 +1217,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>1962</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Källan N, Vb</t>
+          <t>Ängeskälen NV, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>720125</v>
+        <v>720066</v>
       </c>
       <c r="R7" t="n">
-        <v>7214439</v>
+        <v>7214477</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1316,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122748083</v>
+        <v>122748107</v>
       </c>
       <c r="B8" t="n">
-        <v>89998</v>
+        <v>92238</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,38 +1323,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Källan N, Vb</t>
+          <t>Salaligan N, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>720125</v>
+        <v>720065</v>
       </c>
       <c r="R8" t="n">
-        <v>7214437</v>
+        <v>7214297</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122748107</v>
+        <v>122748067</v>
       </c>
       <c r="B9" t="n">
-        <v>92236</v>
+        <v>82558</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,38 +1429,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Salaligan N, Vb</t>
+          <t>Hocklet N, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720065</v>
+        <v>720030</v>
       </c>
       <c r="R9" t="n">
-        <v>7214297</v>
+        <v>7214500</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1498,6 +1493,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ca 20 cm i diameter</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1528,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122748069</v>
+        <v>122748064</v>
       </c>
       <c r="B10" t="n">
-        <v>79754</v>
+        <v>79756</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>720039</v>
+        <v>720010</v>
       </c>
       <c r="R10" t="n">
-        <v>7214502</v>
+        <v>7214517</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1634,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122748064</v>
+        <v>122748085</v>
       </c>
       <c r="B11" t="n">
-        <v>79754</v>
+        <v>90922</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1650,34 +1650,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6456</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hocklet N, Vb</t>
+          <t>Källan N, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>720010</v>
+        <v>720125</v>
       </c>
       <c r="R11" t="n">
-        <v>7214517</v>
+        <v>7214439</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1740,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122748040</v>
+        <v>122748069</v>
       </c>
       <c r="B12" t="n">
-        <v>89998</v>
+        <v>79756</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1962</v>
+        <v>6456</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ängeskälen NV, Vb</t>
+          <t>Hocklet N, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>720066</v>
+        <v>720039</v>
       </c>
       <c r="R12" t="n">
-        <v>7214477</v>
+        <v>7214502</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 50261-2024 artfynd.xlsx
+++ b/artfynd/A 50261-2024 artfynd.xlsx
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122748104</v>
+        <v>122748067</v>
       </c>
       <c r="B2" t="n">
-        <v>92238</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Salaligan N, Vb</t>
+          <t>Hocklet N, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>720064</v>
+        <v>720030</v>
       </c>
       <c r="R2" t="n">
-        <v>7214317</v>
+        <v>7214500</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,6 +748,11 @@
           <t>2024-10-15</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ca 20 cm i diameter</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -775,56 +775,51 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122748055</v>
+        <v>122748040</v>
       </c>
       <c r="B3" t="n">
-        <v>98370</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1962</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ängeskälen V, Vb</t>
+          <t>Ängeskälen NV, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>719987</v>
+        <v>720066</v>
       </c>
       <c r="R3" t="n">
-        <v>7214787</v>
+        <v>7214477</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,43 +876,38 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122748065</v>
+        <v>122748076</v>
       </c>
       <c r="B4" t="n">
-        <v>79756</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6456</v>
+        <v>1962</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +917,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720012</v>
+        <v>720162</v>
       </c>
       <c r="R4" t="n">
-        <v>7214506</v>
+        <v>7214448</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,7 +977,7 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -996,12 +986,7 @@
         <v>122748083</v>
       </c>
       <c r="B5" t="n">
-        <v>90000</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,21 +1078,16 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122748076</v>
+        <v>122748104</v>
       </c>
       <c r="B6" t="n">
-        <v>90000</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1115,34 +1095,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tretjärnarna V, Vb</t>
+          <t>Salaligan N, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720162</v>
+        <v>720064</v>
       </c>
       <c r="R6" t="n">
-        <v>7214448</v>
+        <v>7214317</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1199,21 +1179,16 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122748040</v>
+        <v>122748107</v>
       </c>
       <c r="B7" t="n">
-        <v>90000</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,34 +1196,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ängeskälen NV, Vb</t>
+          <t>Salaligan N, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>720066</v>
+        <v>720065</v>
       </c>
       <c r="R7" t="n">
-        <v>7214477</v>
+        <v>7214297</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,21 +1280,16 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122748107</v>
+        <v>122748085</v>
       </c>
       <c r="B8" t="n">
-        <v>92238</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1327,34 +1297,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Salaligan N, Vb</t>
+          <t>Källan N, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>720065</v>
+        <v>720125</v>
       </c>
       <c r="R8" t="n">
-        <v>7214297</v>
+        <v>7214439</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1411,43 +1381,38 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122748067</v>
+        <v>122748064</v>
       </c>
       <c r="B9" t="n">
-        <v>82558</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>6456</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1422,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720030</v>
+        <v>720010</v>
       </c>
       <c r="R9" t="n">
-        <v>7214500</v>
+        <v>7214517</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,11 +1460,6 @@
           <t>2024-10-15</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ca 20 cm i diameter</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1522,21 +1482,16 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122748064</v>
+        <v>122748065</v>
       </c>
       <c r="B10" t="n">
-        <v>79756</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1564,14 +1519,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hocklet N, Vb</t>
+          <t>Tretjärnarna V, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>720010</v>
+        <v>720012</v>
       </c>
       <c r="R10" t="n">
-        <v>7214517</v>
+        <v>7214506</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1628,21 +1583,16 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122748085</v>
+        <v>122748069</v>
       </c>
       <c r="B11" t="n">
-        <v>90922</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1650,34 +1600,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>6456</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Källan N, Vb</t>
+          <t>Hocklet N, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>720125</v>
+        <v>720039</v>
       </c>
       <c r="R11" t="n">
-        <v>7214439</v>
+        <v>7214502</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1734,56 +1684,51 @@
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122748069</v>
+        <v>122748055</v>
       </c>
       <c r="B12" t="n">
-        <v>79756</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hocklet N, Vb</t>
+          <t>Ängeskälen V, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>720039</v>
+        <v>719987</v>
       </c>
       <c r="R12" t="n">
-        <v>7214502</v>
+        <v>7214787</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1840,7 +1785,7 @@
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
